--- a/lib/asbestos/asbestos-template.xlsx
+++ b/lib/asbestos/asbestos-template.xlsx
@@ -1119,6 +1119,104 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -1382,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CT37"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
@@ -1394,12 +1492,12 @@
     <col min="38" max="16322" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="29.25" customHeight="1" spans="3:88" x14ac:dyDescent="0.25">
+    <row r="2" ht="29.25" customHeight="1" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1432,7 +1530,7 @@
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
     </row>
-    <row r="3" ht="24.9" customHeight="1" spans="16:92" x14ac:dyDescent="0.25">
+    <row r="3" ht="24.9" customHeight="1" spans="16:36" x14ac:dyDescent="0.25">
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
@@ -1460,7 +1558,7 @@
       <c r="AI3" s="15"/>
       <c r="AJ3" s="16"/>
     </row>
-    <row r="4" ht="24.9" customHeight="1" spans="3:92" x14ac:dyDescent="0.25">
+    <row r="4" ht="24.9" customHeight="1" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C4" s="17" t="s">
         <v>8</v>
       </c>
@@ -1503,7 +1601,7 @@
       </c>
       <c r="AJ4" s="26"/>
     </row>
-    <row r="5" ht="24.9" customHeight="1" spans="3:92" x14ac:dyDescent="0.25">
+    <row r="5" ht="24.9" customHeight="1" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
       <c r="E5" s="27"/>
@@ -1546,7 +1644,7 @@
       </c>
       <c r="AJ5" s="26"/>
     </row>
-    <row r="6" ht="24.9" customHeight="1" spans="3:88" x14ac:dyDescent="0.25">
+    <row r="6" ht="24.9" customHeight="1" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C6" s="34"/>
       <c r="D6" s="35"/>
       <c r="E6" s="36"/>
@@ -1589,13 +1687,13 @@
       <c r="AI6" s="19"/>
       <c r="AJ6" s="43"/>
     </row>
-    <row r="7" ht="19.5" customHeight="1" spans="4:88" x14ac:dyDescent="0.25">
+    <row r="7" ht="19.5" customHeight="1" spans="4:25" x14ac:dyDescent="0.25">
       <c r="D7" s="44" t="s">
         <v>22</v>
       </c>
       <c r="Y7" s="4"/>
     </row>
-    <row r="8" ht="19.5" customHeight="1" spans="4:82" x14ac:dyDescent="0.25">
+    <row r="8" ht="19.5" customHeight="1" spans="4:35" x14ac:dyDescent="0.25">
       <c r="D8" s="44" t="s">
         <v>23</v>
       </c>
@@ -1632,7 +1730,7 @@
       <c r="AH8" s="9"/>
       <c r="AI8" s="9"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1" spans="4:95" x14ac:dyDescent="0.25">
+    <row r="9" ht="19.5" customHeight="1" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D9" s="44" t="s">
         <v>25</v>
       </c>
@@ -1661,12 +1759,12 @@
       <c r="AA9" s="44"/>
       <c r="AC9" s="46"/>
     </row>
-    <row r="10" ht="19.5" customHeight="1" spans="4:95" x14ac:dyDescent="0.25">
+    <row r="10" ht="19.5" customHeight="1" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" ht="14.1" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" ht="14.1" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
         <v>27</v>
       </c>
@@ -1756,7 +1854,7 @@
       </c>
       <c r="AJ11" s="52"/>
     </row>
-    <row r="12" ht="14.1" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" ht="14.1" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="53"/>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -1844,7 +1942,7 @@
       </c>
       <c r="AJ12" s="57"/>
     </row>
-    <row r="13" ht="29.25" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" ht="29.25" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>30</v>
       </c>
@@ -1950,7 +2048,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="14" ht="14.25" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
       <c r="B14" s="65" t="s">
         <v>34</v>
@@ -1992,7 +2090,7 @@
       <c r="AI14" s="68"/>
       <c r="AJ14" s="72"/>
     </row>
-    <row r="15" ht="24.75" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="15" ht="24.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="64"/>
       <c r="B15" s="73">
         <v>1</v>
@@ -2032,7 +2130,7 @@
       <c r="AI15" s="76"/>
       <c r="AJ15" s="83"/>
     </row>
-    <row r="16" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="16" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="64"/>
       <c r="B16" s="84">
         <v>2</v>
@@ -2072,7 +2170,7 @@
       <c r="AI16" s="81"/>
       <c r="AJ16" s="90"/>
     </row>
-    <row r="17" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="17" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="64"/>
       <c r="B17" s="84">
         <v>3</v>
@@ -2112,7 +2210,7 @@
       <c r="AI17" s="81"/>
       <c r="AJ17" s="91"/>
     </row>
-    <row r="18" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="18" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="64"/>
       <c r="B18" s="84">
         <v>4</v>
@@ -2152,7 +2250,7 @@
       <c r="AI18" s="81"/>
       <c r="AJ18" s="91"/>
     </row>
-    <row r="19" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="19" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="64"/>
       <c r="B19" s="84">
         <v>5</v>
@@ -2192,7 +2290,7 @@
       <c r="AI19" s="81"/>
       <c r="AJ19" s="90"/>
     </row>
-    <row r="20" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="20" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="64"/>
       <c r="B20" s="84">
         <v>6</v>
@@ -2232,7 +2330,7 @@
       <c r="AI20" s="81"/>
       <c r="AJ20" s="90"/>
     </row>
-    <row r="21" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="21" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="64"/>
       <c r="B21" s="84">
         <v>7</v>
@@ -2272,7 +2370,7 @@
       <c r="AI21" s="81"/>
       <c r="AJ21" s="91"/>
     </row>
-    <row r="22" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="22" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="64"/>
       <c r="B22" s="84">
         <v>8</v>
@@ -2312,7 +2410,7 @@
       <c r="AI22" s="81"/>
       <c r="AJ22" s="90"/>
     </row>
-    <row r="23" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="23" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="64"/>
       <c r="B23" s="84">
         <v>9</v>
@@ -2352,7 +2450,7 @@
       <c r="AI23" s="81"/>
       <c r="AJ23" s="90"/>
     </row>
-    <row r="24" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="24" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="64"/>
       <c r="B24" s="84">
         <v>10</v>
@@ -2392,7 +2490,7 @@
       <c r="AI24" s="81"/>
       <c r="AJ24" s="90"/>
     </row>
-    <row r="25" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="25" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="64"/>
       <c r="B25" s="84">
         <v>11</v>
@@ -2432,7 +2530,7 @@
       <c r="AI25" s="81"/>
       <c r="AJ25" s="90"/>
     </row>
-    <row r="26" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="26" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="64"/>
       <c r="B26" s="84">
         <v>12</v>
@@ -2472,7 +2570,7 @@
       <c r="AI26" s="81"/>
       <c r="AJ26" s="90"/>
     </row>
-    <row r="27" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="27" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="64"/>
       <c r="B27" s="84">
         <v>13</v>
@@ -2512,7 +2610,7 @@
       <c r="AI27" s="81"/>
       <c r="AJ27" s="90"/>
     </row>
-    <row r="28" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="28" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="64"/>
       <c r="B28" s="84">
         <v>14</v>
@@ -2552,7 +2650,7 @@
       <c r="AI28" s="81"/>
       <c r="AJ28" s="90"/>
     </row>
-    <row r="29" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="29" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="64"/>
       <c r="B29" s="84">
         <v>15</v>
@@ -2592,7 +2690,7 @@
       <c r="AI29" s="81"/>
       <c r="AJ29" s="90"/>
     </row>
-    <row r="30" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="30" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="64"/>
       <c r="B30" s="84">
         <v>16</v>
@@ -2632,7 +2730,7 @@
       <c r="AI30" s="81"/>
       <c r="AJ30" s="90"/>
     </row>
-    <row r="31" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="31" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="64"/>
       <c r="B31" s="84">
         <v>17</v>
@@ -2672,7 +2770,7 @@
       <c r="AI31" s="81"/>
       <c r="AJ31" s="90"/>
     </row>
-    <row r="32" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="32" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="64"/>
       <c r="B32" s="84">
         <v>18</v>
@@ -2712,7 +2810,7 @@
       <c r="AI32" s="81"/>
       <c r="AJ32" s="90"/>
     </row>
-    <row r="33" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="33" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="64"/>
       <c r="B33" s="84">
         <v>19</v>
@@ -2752,7 +2850,7 @@
       <c r="AI33" s="81"/>
       <c r="AJ33" s="91"/>
     </row>
-    <row r="34" ht="24.9" customHeight="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="34" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="64"/>
       <c r="B34" s="84">
         <v>20</v>
@@ -3008,12 +3106,13 @@
   </mergeCells>
   <pageMargins left="0.4330708661417323" right="0" top="0.4330708661417323" bottom="0.1968503937007874" header="0.4330708661417323" footer="0.1968503937007874"/>
   <pageSetup paperSize="8" orientation="landscape" horizontalDpi="300" verticalDpi="300" scale="89" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CS37"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
@@ -3025,8 +3124,8 @@
     <col min="38" max="16323" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="38:39" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="29.25" customHeight="1" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="29.25" customHeight="1" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3059,7 +3158,7 @@
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
     </row>
-    <row r="3" ht="24.9" customHeight="1" spans="16:39" x14ac:dyDescent="0.25">
+    <row r="3" ht="24.9" customHeight="1" spans="16:36" x14ac:dyDescent="0.25">
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
@@ -3087,7 +3186,7 @@
       <c r="AI3" s="15"/>
       <c r="AJ3" s="16"/>
     </row>
-    <row r="4" ht="24.9" customHeight="1" spans="3:83" x14ac:dyDescent="0.25">
+    <row r="4" ht="24.9" customHeight="1" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C4" s="17" t="str">
         <f>石綿作業従事者記録_上!C4</f>
         <v>管轄工事会社:</v>
@@ -3131,7 +3230,7 @@
       </c>
       <c r="AJ4" s="26"/>
     </row>
-    <row r="5" ht="24.9" customHeight="1" spans="3:83" x14ac:dyDescent="0.25">
+    <row r="5" ht="24.9" customHeight="1" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C5" s="34"/>
       <c r="D5" s="116"/>
       <c r="E5" s="116"/>
@@ -3174,7 +3273,7 @@
       </c>
       <c r="AJ5" s="26"/>
     </row>
-    <row r="6" ht="24.9" customHeight="1" spans="3:83" x14ac:dyDescent="0.25">
+    <row r="6" ht="24.9" customHeight="1" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C6" s="34"/>
       <c r="D6" s="35"/>
       <c r="E6" s="36"/>
@@ -3217,13 +3316,13 @@
       <c r="AI6" s="19"/>
       <c r="AJ6" s="43"/>
     </row>
-    <row r="7" ht="19.5" customHeight="1" spans="4:39" x14ac:dyDescent="0.25">
+    <row r="7" ht="19.5" customHeight="1" spans="4:25" x14ac:dyDescent="0.25">
       <c r="D7" s="44" t="s">
         <v>22</v>
       </c>
       <c r="Y7" s="4"/>
     </row>
-    <row r="8" ht="19.5" customHeight="1" spans="4:39" x14ac:dyDescent="0.25">
+    <row r="8" ht="19.5" customHeight="1" spans="4:35" x14ac:dyDescent="0.25">
       <c r="D8" s="44" t="s">
         <v>23</v>
       </c>
@@ -3289,12 +3388,12 @@
       <c r="AA9" s="44"/>
       <c r="AC9" s="46"/>
     </row>
-    <row r="10" ht="19.5" customHeight="1" spans="4:38" x14ac:dyDescent="0.25">
+    <row r="10" ht="19.5" customHeight="1" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" ht="14.1" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" ht="14.1" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
         <v>27</v>
       </c>
@@ -3464,7 +3563,7 @@
       <c r="AI12" s="56"/>
       <c r="AJ12" s="57"/>
     </row>
-    <row r="13" ht="29.25" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" ht="29.25" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>30</v>
       </c>
@@ -3570,7 +3669,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="14" ht="14.25" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
       <c r="B14" s="65" t="s">
         <v>34</v>
@@ -3612,7 +3711,7 @@
       <c r="AI14" s="68"/>
       <c r="AJ14" s="72"/>
     </row>
-    <row r="15" ht="24.75" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="15" ht="24.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="64"/>
       <c r="B15" s="73">
         <v>1</v>
@@ -3652,7 +3751,7 @@
       <c r="AI15" s="76"/>
       <c r="AJ15" s="83"/>
     </row>
-    <row r="16" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="16" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="64"/>
       <c r="B16" s="84">
         <v>2</v>
@@ -3692,7 +3791,7 @@
       <c r="AI16" s="81"/>
       <c r="AJ16" s="90"/>
     </row>
-    <row r="17" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="17" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="64"/>
       <c r="B17" s="84">
         <v>3</v>
@@ -3732,7 +3831,7 @@
       <c r="AI17" s="81"/>
       <c r="AJ17" s="91"/>
     </row>
-    <row r="18" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="18" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="64"/>
       <c r="B18" s="84">
         <v>4</v>
@@ -3772,7 +3871,7 @@
       <c r="AI18" s="81"/>
       <c r="AJ18" s="91"/>
     </row>
-    <row r="19" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="19" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="64"/>
       <c r="B19" s="84">
         <v>5</v>
@@ -3812,7 +3911,7 @@
       <c r="AI19" s="81"/>
       <c r="AJ19" s="90"/>
     </row>
-    <row r="20" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="20" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="64"/>
       <c r="B20" s="84">
         <v>6</v>
@@ -3852,7 +3951,7 @@
       <c r="AI20" s="81"/>
       <c r="AJ20" s="90"/>
     </row>
-    <row r="21" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="21" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="64"/>
       <c r="B21" s="84">
         <v>7</v>
@@ -3892,7 +3991,7 @@
       <c r="AI21" s="81"/>
       <c r="AJ21" s="91"/>
     </row>
-    <row r="22" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="22" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="64"/>
       <c r="B22" s="84">
         <v>8</v>
@@ -3932,7 +4031,7 @@
       <c r="AI22" s="81"/>
       <c r="AJ22" s="90"/>
     </row>
-    <row r="23" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="23" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="64"/>
       <c r="B23" s="84">
         <v>9</v>
@@ -3972,7 +4071,7 @@
       <c r="AI23" s="81"/>
       <c r="AJ23" s="90"/>
     </row>
-    <row r="24" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="24" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="64"/>
       <c r="B24" s="84">
         <v>10</v>
@@ -4012,7 +4111,7 @@
       <c r="AI24" s="81"/>
       <c r="AJ24" s="90"/>
     </row>
-    <row r="25" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="25" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="64"/>
       <c r="B25" s="84">
         <v>11</v>
@@ -4052,7 +4151,7 @@
       <c r="AI25" s="81"/>
       <c r="AJ25" s="90"/>
     </row>
-    <row r="26" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="26" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="64"/>
       <c r="B26" s="84">
         <v>12</v>
@@ -4092,7 +4191,7 @@
       <c r="AI26" s="81"/>
       <c r="AJ26" s="90"/>
     </row>
-    <row r="27" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="27" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="64"/>
       <c r="B27" s="84">
         <v>13</v>
@@ -4132,7 +4231,7 @@
       <c r="AI27" s="81"/>
       <c r="AJ27" s="90"/>
     </row>
-    <row r="28" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="28" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="64"/>
       <c r="B28" s="84">
         <v>14</v>
@@ -4172,7 +4271,7 @@
       <c r="AI28" s="81"/>
       <c r="AJ28" s="90"/>
     </row>
-    <row r="29" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="29" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="64"/>
       <c r="B29" s="84">
         <v>15</v>
@@ -4212,7 +4311,7 @@
       <c r="AI29" s="81"/>
       <c r="AJ29" s="90"/>
     </row>
-    <row r="30" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="30" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="64"/>
       <c r="B30" s="84">
         <v>16</v>
@@ -4252,7 +4351,7 @@
       <c r="AI30" s="81"/>
       <c r="AJ30" s="90"/>
     </row>
-    <row r="31" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="31" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="64"/>
       <c r="B31" s="84">
         <v>17</v>
@@ -4292,7 +4391,7 @@
       <c r="AI31" s="81"/>
       <c r="AJ31" s="90"/>
     </row>
-    <row r="32" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="32" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="64"/>
       <c r="B32" s="84">
         <v>18</v>
@@ -4332,7 +4431,7 @@
       <c r="AI32" s="81"/>
       <c r="AJ32" s="90"/>
     </row>
-    <row r="33" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="33" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="64"/>
       <c r="B33" s="84">
         <v>19</v>
@@ -4372,7 +4471,7 @@
       <c r="AI33" s="81"/>
       <c r="AJ33" s="91"/>
     </row>
-    <row r="34" ht="24.9" customHeight="1" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="34" ht="24.9" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="64"/>
       <c r="B34" s="84">
         <v>20</v>
@@ -4628,5 +4727,6 @@
   </mergeCells>
   <pageMargins left="0.4330708661417323" right="0" top="0.4330708661417323" bottom="0.1968503937007874" header="0.4330708661417323" footer="0.1968503937007874"/>
   <pageSetup paperSize="8" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="89" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>